--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -464,8 +464,7 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGCV
-- WGISS</t>
+- WGCV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -493,8 +492,7 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGCV
-- WGClimate</t>
+- WGCV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -526,8 +524,7 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGCV
-- WGISS</t>
+- WGCV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -551,65 +548,65 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Instrument Data</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>- core
 - to be approved
 - calval ingest
 - WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sensor Data, Sensor Data Record</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
 - [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
 - [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
 - NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,24 +470,93 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
+          <t>- ISO 19116:2004(E)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -495,15 +564,43 @@
 - WGCV</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Process of assessing, by independent means, the quality of data products derived from system outputs.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>- (1) CEOS/ISO:19159 [RD10]; (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (3) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (4) NIST [RD15]; (5) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]
 - RD10:SO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
@@ -513,103 +610,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Instrument Data</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sensor Data, Sensor Data Record</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
